--- a/Result/checksun/金融業.xlsx
+++ b/Result/checksun/金融業.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1668,37 +1668,37 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1897,11 +1897,15 @@
           <t>98.08000000000001</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>96.81999999999999</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>92.25</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>96.82</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>92.25</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2639,12 +2643,12 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -2654,37 +2658,37 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2883,11 +2887,15 @@
           <t>97.55999999999999</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>96.67</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>91.84999999999999</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>96.67</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>91.85</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3625,12 +3633,12 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -3640,37 +3648,37 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3869,11 +3877,15 @@
           <t>97.06</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>96.52</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>91.45</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>96.52</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>91.45</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4606,17 +4618,17 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -4626,37 +4638,37 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4855,11 +4867,15 @@
           <t>96.66</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>96.34</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>91.04000000000001</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>96.34</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>91.04</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5592,17 +5608,17 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -5612,37 +5628,37 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5841,11 +5857,15 @@
           <t>96.35</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>96.16</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>90.64</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>96.16</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>90.64</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6573,62 +6593,62 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6827,11 +6847,15 @@
           <t>95.84</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>95.95999999999999</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>90.26000000000001</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>95.96</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>90.26</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7584,7 +7608,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7599,22 +7623,22 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7813,11 +7837,15 @@
           <t>95.5</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>89.87</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>95.7</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>89.87</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8570,7 +8598,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8585,22 +8613,22 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8799,11 +8827,15 @@
           <t>95.39</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>95.70999999999999</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>89.53</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>95.71</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>89.53</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9556,7 +9588,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9571,22 +9603,22 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9785,11 +9817,15 @@
           <t>95.34</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>95.51000000000001</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>89.18000000000001</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>95.51</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>89.18</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10522,57 +10558,57 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10771,11 +10807,15 @@
           <t>15.835</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>14.84</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>14.84</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11508,57 +11548,57 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11757,11 +11797,15 @@
           <t>15.765</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>14.81</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>15.46</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>14.81</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12489,62 +12533,62 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12743,11 +12787,15 @@
           <t>15.68</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>15.42</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>14.78</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>15.42</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>14.78</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13475,62 +13523,62 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13729,11 +13777,15 @@
           <t>15.595</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>15.37</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>14.74</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>15.37</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>14.74</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14461,62 +14513,62 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14715,11 +14767,15 @@
           <t>15.515</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>14.7</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>15.33</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15447,62 +15503,62 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15701,11 +15757,15 @@
           <t>15.45</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>14.68</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>15.28</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>14.68</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16433,62 +16493,62 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16687,11 +16747,15 @@
           <t>15.375</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>15.23</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>14.66</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>15.23</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>14.66</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17444,37 +17508,37 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17673,11 +17737,15 @@
           <t>15.32</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>15.17</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>14.64</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>15.17</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>14.64</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18430,37 +18498,37 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18659,11 +18727,15 @@
           <t>15.255</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>14.63</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>15.11</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>14.63</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19416,7 +19488,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -19431,22 +19503,22 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -19466,47 +19538,47 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>169740.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>-57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>-152000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK20" t="inlineStr">
         <is>
-          <t>-39260.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
@@ -19645,11 +19717,15 @@
           <t>86.58000000000001</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>85.68000000000001</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>85.38</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>85.68</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>85.38</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20402,7 +20478,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -20412,27 +20488,27 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -20452,47 +20528,47 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>169740.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>-57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>-152000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK21" t="inlineStr">
         <is>
-          <t>-39260.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
@@ -20631,11 +20707,15 @@
           <t>86.61</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>85.76000000000001</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>85.45</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>85.76</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>85.45</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21388,7 +21468,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -21398,27 +21478,27 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -21438,47 +21518,47 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>169740.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>-57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>-152000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK22" t="inlineStr">
         <is>
-          <t>-39260.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
@@ -21617,11 +21697,15 @@
           <t>86.57000000000001</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>85.48999999999999</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>85.49</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22374,32 +22458,32 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -22424,47 +22508,47 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>169740.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>-57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>-152000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK23" t="inlineStr">
         <is>
-          <t>-39260.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
@@ -22603,11 +22687,15 @@
           <t>86.59</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>85.90000000000001</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>85.5</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>85.9</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23360,32 +23448,32 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -23410,47 +23498,47 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>169740.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>-57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>-152000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK24" t="inlineStr">
         <is>
-          <t>-39260.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM24" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
@@ -23589,11 +23677,15 @@
           <t>86.48</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>85.53</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>85.71</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>85.53</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24341,37 +24433,37 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -24396,47 +24488,47 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>169740.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>-57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>-152000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
-          <t>-39260.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM25" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
@@ -24575,11 +24667,15 @@
           <t>86.28</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>85.51000000000001</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>85.92</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>85.51</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>85.92</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25327,37 +25423,37 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -25382,47 +25478,47 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>169740.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>-57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>-152000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK26" t="inlineStr">
         <is>
-          <t>-39260.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM26" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
@@ -25561,11 +25657,15 @@
           <t>86.07000000000001</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>85.28</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>86.29000000000001</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>85.28</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>86.29</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26313,37 +26413,37 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -26368,47 +26468,47 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>169740.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>-57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>-152000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK27" t="inlineStr">
         <is>
-          <t>-39260.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM27" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
@@ -26547,11 +26647,15 @@
           <t>85.57000000000001</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>84.98</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>86.59999999999999</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>84.98</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>86.6</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27299,32 +27403,32 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -27354,47 +27458,47 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>169740.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>-57000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>-152000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK28" t="inlineStr">
         <is>
-          <t>-39260.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM28" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
@@ -27533,11 +27637,15 @@
           <t>85.07000000000001</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>84.72</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>86.95</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>84.72</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>86.95</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28280,47 +28388,47 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28519,11 +28627,15 @@
           <t>43.15</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>38.84</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>42.84</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>38.84</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29266,47 +29378,47 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29505,11 +29617,15 @@
           <t>43.45999999999999</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>38.75</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>38.75</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30247,52 +30363,52 @@
       </c>
       <c r="AS31" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT31" t="inlineStr">
+      <c r="AY31" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30491,11 +30607,15 @@
           <t>43.71</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>42.57</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>38.66</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>42.57</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>38.66</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31233,52 +31353,52 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AT32" t="inlineStr">
+      <c r="AY32" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31477,11 +31597,15 @@
           <t>44.005</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>42.42</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>38.55</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>42.42</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>38.55</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32214,57 +32338,57 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AS33" t="inlineStr">
+      <c r="AX33" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AT33" t="inlineStr">
+      <c r="AY33" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32463,11 +32587,15 @@
           <t>44.2</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>42.35</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>38.47</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>42.35</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>38.47</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33200,57 +33328,57 @@
       </c>
       <c r="AR34" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS34" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AT34" t="inlineStr">
+      <c r="AY34" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33449,11 +33577,15 @@
           <t>44.3</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>42.23</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>38.42</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>42.23</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>38.42</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34181,62 +34313,62 @@
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR35" t="inlineStr">
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS35" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT35" t="inlineStr">
+      <c r="AY35" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34435,11 +34567,15 @@
           <t>44.345</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>42.08</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>38.36</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>42.08</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>38.36</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35167,62 +35303,62 @@
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR36" t="inlineStr">
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS36" t="inlineStr">
+      <c r="AX36" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT36" t="inlineStr">
+      <c r="AY36" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35421,11 +35557,15 @@
           <t>44.08499999999999</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>41.76</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>38.22</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>41.76</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>38.22</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36153,62 +36293,62 @@
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR37" t="inlineStr">
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS37" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT37" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36407,11 +36547,15 @@
           <t>43.63</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>41.44</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>38.07</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>41.44</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>38.07</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
@@ -37164,7 +37308,7 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -37179,22 +37323,22 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -37393,11 +37537,15 @@
           <t>20.61</t>
         </is>
       </c>
-      <c r="CQ38" t="n">
-        <v>20.63</v>
-      </c>
-      <c r="CR38" t="n">
-        <v>20.76</v>
+      <c r="CQ38" t="inlineStr">
+        <is>
+          <t>20.63</t>
+        </is>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>20.76</t>
+        </is>
       </c>
       <c r="CS38" t="inlineStr">
         <is>
@@ -38150,7 +38298,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -38165,22 +38313,22 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -38379,11 +38527,15 @@
           <t>20.61</t>
         </is>
       </c>
-      <c r="CQ39" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>20.79</v>
+      <c r="CQ39" t="inlineStr">
+        <is>
+          <t>20.64</t>
+        </is>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>20.79</t>
+        </is>
       </c>
       <c r="CS39" t="inlineStr">
         <is>
@@ -39136,7 +39288,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -39151,22 +39303,22 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -39365,11 +39517,15 @@
           <t>20.6</t>
         </is>
       </c>
-      <c r="CQ40" t="n">
-        <v>20.66</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>20.81</v>
+      <c r="CQ40" t="inlineStr">
+        <is>
+          <t>20.66</t>
+        </is>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>20.81</t>
+        </is>
       </c>
       <c r="CS40" t="inlineStr">
         <is>
@@ -40122,7 +40278,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -40137,22 +40293,22 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -40351,11 +40507,15 @@
           <t>20.565</t>
         </is>
       </c>
-      <c r="CQ41" t="n">
-        <v>20.66</v>
-      </c>
-      <c r="CR41" t="n">
-        <v>20.83</v>
+      <c r="CQ41" t="inlineStr">
+        <is>
+          <t>20.66</t>
+        </is>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>20.83</t>
+        </is>
       </c>
       <c r="CS41" t="inlineStr">
         <is>
@@ -41108,7 +41268,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -41123,22 +41283,22 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -41337,11 +41497,15 @@
           <t>20.545</t>
         </is>
       </c>
-      <c r="CQ42" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>20.86</v>
+      <c r="CQ42" t="inlineStr">
+        <is>
+          <t>20.68</t>
+        </is>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>20.86</t>
+        </is>
       </c>
       <c r="CS42" t="inlineStr">
         <is>
@@ -42094,7 +42258,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -42109,22 +42273,22 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -42323,11 +42487,15 @@
           <t>20.545</t>
         </is>
       </c>
-      <c r="CQ43" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>20.88</v>
+      <c r="CQ43" t="inlineStr">
+        <is>
+          <t>20.69</t>
+        </is>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>20.88</t>
+        </is>
       </c>
       <c r="CS43" t="inlineStr">
         <is>
@@ -43080,7 +43248,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -43095,22 +43263,22 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -43309,11 +43477,15 @@
           <t>20.545</t>
         </is>
       </c>
-      <c r="CQ44" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>20.9</v>
+      <c r="CQ44" t="inlineStr">
+        <is>
+          <t>20.68</t>
+        </is>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
       </c>
       <c r="CS44" t="inlineStr">
         <is>
@@ -44066,7 +44238,7 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
@@ -44081,22 +44253,22 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
@@ -44295,11 +44467,15 @@
           <t>20.555</t>
         </is>
       </c>
-      <c r="CQ45" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>20.92</v>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>20.68</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>20.92</t>
+        </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
@@ -45052,7 +45228,7 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -45067,22 +45243,22 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -45281,11 +45457,15 @@
           <t>20.575</t>
         </is>
       </c>
-      <c r="CQ46" t="n">
-        <v>20.66</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>20.95</v>
+      <c r="CQ46" t="inlineStr">
+        <is>
+          <t>20.66</t>
+        </is>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>20.95</t>
+        </is>
       </c>
       <c r="CS46" t="inlineStr">
         <is>
@@ -46028,7 +46208,7 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
@@ -46038,37 +46218,37 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
@@ -46267,11 +46447,15 @@
           <t>23.6</t>
         </is>
       </c>
-      <c r="CQ47" t="n">
-        <v>22.96</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>21.38</v>
+      <c r="CQ47" t="inlineStr">
+        <is>
+          <t>22.96</t>
+        </is>
+      </c>
+      <c r="CR47" t="inlineStr">
+        <is>
+          <t>21.38</t>
+        </is>
       </c>
       <c r="CS47" t="inlineStr">
         <is>
@@ -47014,7 +47198,7 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
@@ -47024,37 +47208,37 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
@@ -47253,11 +47437,15 @@
           <t>23.42</t>
         </is>
       </c>
-      <c r="CQ48" t="n">
-        <v>22.82</v>
-      </c>
-      <c r="CR48" t="n">
-        <v>21.4</v>
+      <c r="CQ48" t="inlineStr">
+        <is>
+          <t>22.82</t>
+        </is>
+      </c>
+      <c r="CR48" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
       </c>
       <c r="CS48" t="inlineStr">
         <is>
@@ -47995,12 +48183,12 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
@@ -48010,37 +48198,37 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
@@ -48239,11 +48427,15 @@
           <t>23.24</t>
         </is>
       </c>
-      <c r="CQ49" t="n">
-        <v>22.71</v>
-      </c>
-      <c r="CR49" t="n">
-        <v>21.41</v>
+      <c r="CQ49" t="inlineStr">
+        <is>
+          <t>22.71</t>
+        </is>
+      </c>
+      <c r="CR49" t="inlineStr">
+        <is>
+          <t>21.41</t>
+        </is>
       </c>
       <c r="CS49" t="inlineStr">
         <is>
@@ -48981,12 +49173,12 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
@@ -48996,37 +49188,37 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
@@ -49225,11 +49417,15 @@
           <t>23.065</t>
         </is>
       </c>
-      <c r="CQ50" t="n">
-        <v>22.56</v>
-      </c>
-      <c r="CR50" t="n">
-        <v>21.41</v>
+      <c r="CQ50" t="inlineStr">
+        <is>
+          <t>22.56</t>
+        </is>
+      </c>
+      <c r="CR50" t="inlineStr">
+        <is>
+          <t>21.41</t>
+        </is>
       </c>
       <c r="CS50" t="inlineStr">
         <is>
@@ -49962,17 +50158,17 @@
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
@@ -49982,37 +50178,37 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
@@ -50211,11 +50407,15 @@
           <t>22.94</t>
         </is>
       </c>
-      <c r="CQ51" t="n">
-        <v>22.45</v>
-      </c>
-      <c r="CR51" t="n">
-        <v>21.42</v>
+      <c r="CQ51" t="inlineStr">
+        <is>
+          <t>22.45</t>
+        </is>
+      </c>
+      <c r="CR51" t="inlineStr">
+        <is>
+          <t>21.42</t>
+        </is>
       </c>
       <c r="CS51" t="inlineStr">
         <is>
@@ -50948,17 +51148,17 @@
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
@@ -50968,37 +51168,37 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -51197,11 +51397,15 @@
           <t>22.835</t>
         </is>
       </c>
-      <c r="CQ52" t="n">
-        <v>22.28</v>
-      </c>
-      <c r="CR52" t="n">
-        <v>21.45</v>
+      <c r="CQ52" t="inlineStr">
+        <is>
+          <t>22.28</t>
+        </is>
+      </c>
+      <c r="CR52" t="inlineStr">
+        <is>
+          <t>21.45</t>
+        </is>
       </c>
       <c r="CS52" t="inlineStr">
         <is>
@@ -51929,62 +52133,62 @@
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AT53" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
@@ -52183,11 +52387,15 @@
           <t>22.745</t>
         </is>
       </c>
-      <c r="CQ53" t="n">
-        <v>22.08</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>21.49</v>
+      <c r="CQ53" t="inlineStr">
+        <is>
+          <t>22.08</t>
+        </is>
+      </c>
+      <c r="CR53" t="inlineStr">
+        <is>
+          <t>21.49</t>
+        </is>
       </c>
       <c r="CS53" t="inlineStr">
         <is>
@@ -52935,42 +53143,42 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
@@ -53169,11 +53377,15 @@
           <t>22.695</t>
         </is>
       </c>
-      <c r="CQ54" t="n">
-        <v>21.87</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>21.52</v>
+      <c r="CQ54" t="inlineStr">
+        <is>
+          <t>21.87</t>
+        </is>
+      </c>
+      <c r="CR54" t="inlineStr">
+        <is>
+          <t>21.52</t>
+        </is>
       </c>
       <c r="CS54" t="inlineStr">
         <is>
@@ -53921,42 +54133,42 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
@@ -54155,11 +54367,15 @@
           <t>22.54</t>
         </is>
       </c>
-      <c r="CQ55" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="CR55" t="n">
-        <v>21.57</v>
+      <c r="CQ55" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="CR55" t="inlineStr">
+        <is>
+          <t>21.57</t>
+        </is>
       </c>
       <c r="CS55" t="inlineStr">
         <is>
@@ -54897,52 +55113,52 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AT56" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV56" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
@@ -55141,11 +55357,15 @@
           <t>17.68</t>
         </is>
       </c>
-      <c r="CQ56" t="n">
-        <v>17.37</v>
-      </c>
-      <c r="CR56" t="n">
-        <v>16.4</v>
+      <c r="CQ56" t="inlineStr">
+        <is>
+          <t>17.37</t>
+        </is>
+      </c>
+      <c r="CR56" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
       </c>
       <c r="CS56" t="inlineStr">
         <is>
@@ -55878,57 +56098,57 @@
       </c>
       <c r="AR57" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AS57" t="inlineStr">
+      <c r="AX57" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AT57" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -56127,11 +56347,15 @@
           <t>17.6</t>
         </is>
       </c>
-      <c r="CQ57" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="CR57" t="n">
-        <v>16.38</v>
+      <c r="CQ57" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CR57" t="inlineStr">
+        <is>
+          <t>16.38</t>
+        </is>
       </c>
       <c r="CS57" t="inlineStr">
         <is>
@@ -56864,57 +57088,57 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS58" t="inlineStr">
+      <c r="AX58" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AT58" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV58" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
@@ -57113,11 +57337,15 @@
           <t>17.525</t>
         </is>
       </c>
-      <c r="CQ58" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="CR58" t="n">
-        <v>16.36</v>
+      <c r="CQ58" t="inlineStr">
+        <is>
+          <t>17.25</t>
+        </is>
+      </c>
+      <c r="CR58" t="inlineStr">
+        <is>
+          <t>16.36</t>
+        </is>
       </c>
       <c r="CS58" t="inlineStr">
         <is>
@@ -57845,62 +58073,62 @@
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AT59" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV59" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
@@ -58099,11 +58327,15 @@
           <t>17.465</t>
         </is>
       </c>
-      <c r="CQ59" t="n">
-        <v>17.16</v>
-      </c>
-      <c r="CR59" t="n">
-        <v>16.32</v>
+      <c r="CQ59" t="inlineStr">
+        <is>
+          <t>17.16</t>
+        </is>
+      </c>
+      <c r="CR59" t="inlineStr">
+        <is>
+          <t>16.32</t>
+        </is>
       </c>
       <c r="CS59" t="inlineStr">
         <is>
@@ -58831,62 +59063,62 @@
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR60" t="inlineStr">
+      <c r="AW60" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT60" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV60" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
@@ -59085,11 +59317,15 @@
           <t>17.42</t>
         </is>
       </c>
-      <c r="CQ60" t="n">
-        <v>17.11</v>
-      </c>
-      <c r="CR60" t="n">
-        <v>16.3</v>
+      <c r="CQ60" t="inlineStr">
+        <is>
+          <t>17.11</t>
+        </is>
+      </c>
+      <c r="CR60" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
       </c>
       <c r="CS60" t="inlineStr">
         <is>
@@ -59817,62 +60053,62 @@
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT61" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
@@ -60071,11 +60307,15 @@
           <t>17.375</t>
         </is>
       </c>
-      <c r="CQ61" t="n">
-        <v>17.03</v>
-      </c>
-      <c r="CR61" t="n">
-        <v>16.29</v>
+      <c r="CQ61" t="inlineStr">
+        <is>
+          <t>17.03</t>
+        </is>
+      </c>
+      <c r="CR61" t="inlineStr">
+        <is>
+          <t>16.29</t>
+        </is>
       </c>
       <c r="CS61" t="inlineStr">
         <is>
@@ -60803,62 +61043,62 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AT62" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
@@ -61057,11 +61297,15 @@
           <t>17.335</t>
         </is>
       </c>
-      <c r="CQ62" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="CR62" t="n">
-        <v>16.29</v>
+      <c r="CQ62" t="inlineStr">
+        <is>
+          <t>16.94</t>
+        </is>
+      </c>
+      <c r="CR62" t="inlineStr">
+        <is>
+          <t>16.29</t>
+        </is>
       </c>
       <c r="CS62" t="inlineStr">
         <is>
@@ -61799,52 +62043,52 @@
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
@@ -62043,11 +62287,15 @@
           <t>17.34</t>
         </is>
       </c>
-      <c r="CQ63" t="n">
-        <v>16.82</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>16.27</v>
+      <c r="CQ63" t="inlineStr">
+        <is>
+          <t>16.82</t>
+        </is>
+      </c>
+      <c r="CR63" t="inlineStr">
+        <is>
+          <t>16.27</t>
+        </is>
       </c>
       <c r="CS63" t="inlineStr">
         <is>
@@ -62785,52 +63033,52 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AT64" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV64" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
@@ -63029,11 +63277,15 @@
           <t>17.24</t>
         </is>
       </c>
-      <c r="CQ64" t="n">
-        <v>16.72</v>
-      </c>
-      <c r="CR64" t="n">
-        <v>16.26</v>
+      <c r="CQ64" t="inlineStr">
+        <is>
+          <t>16.72</t>
+        </is>
+      </c>
+      <c r="CR64" t="inlineStr">
+        <is>
+          <t>16.26</t>
+        </is>
       </c>
       <c r="CS64" t="inlineStr">
         <is>
@@ -63786,7 +64038,7 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
@@ -63801,7 +64053,7 @@
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
@@ -63811,12 +64063,12 @@
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
@@ -64015,11 +64267,15 @@
           <t>38.01000000000001</t>
         </is>
       </c>
-      <c r="CQ65" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="CR65" t="n">
-        <v>38.34</v>
+      <c r="CQ65" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="CR65" t="inlineStr">
+        <is>
+          <t>38.34</t>
+        </is>
       </c>
       <c r="CS65" t="inlineStr">
         <is>
@@ -64772,7 +65028,7 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
@@ -64787,7 +65043,7 @@
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
@@ -64797,12 +65053,12 @@
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
@@ -65001,11 +65257,15 @@
           <t>38.035</t>
         </is>
       </c>
-      <c r="CQ66" t="n">
-        <v>38.14</v>
-      </c>
-      <c r="CR66" t="n">
-        <v>38.36</v>
+      <c r="CQ66" t="inlineStr">
+        <is>
+          <t>38.14</t>
+        </is>
+      </c>
+      <c r="CR66" t="inlineStr">
+        <is>
+          <t>38.36</t>
+        </is>
       </c>
       <c r="CS66" t="inlineStr">
         <is>
@@ -65758,7 +66018,7 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
@@ -65773,7 +66033,7 @@
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
@@ -65783,12 +66043,12 @@
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
@@ -65987,11 +66247,15 @@
           <t>38.05499999999999</t>
         </is>
       </c>
-      <c r="CQ67" t="n">
-        <v>38.17</v>
-      </c>
-      <c r="CR67" t="n">
-        <v>38.38</v>
+      <c r="CQ67" t="inlineStr">
+        <is>
+          <t>38.17</t>
+        </is>
+      </c>
+      <c r="CR67" t="inlineStr">
+        <is>
+          <t>38.38</t>
+        </is>
       </c>
       <c r="CS67" t="inlineStr">
         <is>
@@ -66744,7 +67008,7 @@
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
@@ -66759,7 +67023,7 @@
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
@@ -66769,12 +67033,12 @@
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
@@ -66973,11 +67237,15 @@
           <t>38.08</t>
         </is>
       </c>
-      <c r="CQ68" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="CR68" t="n">
-        <v>38.4</v>
+      <c r="CQ68" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CR68" t="inlineStr">
+        <is>
+          <t>38.4</t>
+        </is>
       </c>
       <c r="CS68" t="inlineStr">
         <is>
@@ -67730,7 +67998,7 @@
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
@@ -67745,7 +68013,7 @@
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
@@ -67755,12 +68023,12 @@
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
@@ -67959,11 +68227,15 @@
           <t>38.09999999999999</t>
         </is>
       </c>
-      <c r="CQ69" t="n">
-        <v>38.23</v>
-      </c>
-      <c r="CR69" t="n">
-        <v>38.41</v>
+      <c r="CQ69" t="inlineStr">
+        <is>
+          <t>38.23</t>
+        </is>
+      </c>
+      <c r="CR69" t="inlineStr">
+        <is>
+          <t>38.41</t>
+        </is>
       </c>
       <c r="CS69" t="inlineStr">
         <is>
@@ -68716,7 +68988,7 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
@@ -68731,22 +69003,22 @@
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
@@ -68945,11 +69217,15 @@
           <t>38.095</t>
         </is>
       </c>
-      <c r="CQ70" t="n">
-        <v>38.25</v>
-      </c>
-      <c r="CR70" t="n">
-        <v>38.43</v>
+      <c r="CQ70" t="inlineStr">
+        <is>
+          <t>38.25</t>
+        </is>
+      </c>
+      <c r="CR70" t="inlineStr">
+        <is>
+          <t>38.43</t>
+        </is>
       </c>
       <c r="CS70" t="inlineStr">
         <is>
@@ -69702,7 +69978,7 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
@@ -69717,22 +69993,22 @@
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
@@ -69931,11 +70207,15 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="CQ71" t="n">
-        <v>38.28</v>
-      </c>
-      <c r="CR71" t="n">
-        <v>38.44</v>
+      <c r="CQ71" t="inlineStr">
+        <is>
+          <t>38.28</t>
+        </is>
+      </c>
+      <c r="CR71" t="inlineStr">
+        <is>
+          <t>38.44</t>
+        </is>
       </c>
       <c r="CS71" t="inlineStr">
         <is>
@@ -70688,7 +70968,7 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
@@ -70703,22 +70983,22 @@
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
@@ -70917,11 +71197,15 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="CQ72" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="CR72" t="n">
-        <v>38.45</v>
+      <c r="CQ72" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="CR72" t="inlineStr">
+        <is>
+          <t>38.45</t>
+        </is>
       </c>
       <c r="CS72" t="inlineStr">
         <is>
@@ -71674,7 +71958,7 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
@@ -71689,22 +71973,22 @@
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
@@ -71903,11 +72187,15 @@
           <t>38.09999999999999</t>
         </is>
       </c>
-      <c r="CQ73" t="n">
-        <v>38.32</v>
-      </c>
-      <c r="CR73" t="n">
-        <v>38.46</v>
+      <c r="CQ73" t="inlineStr">
+        <is>
+          <t>38.32</t>
+        </is>
+      </c>
+      <c r="CR73" t="inlineStr">
+        <is>
+          <t>38.46</t>
+        </is>
       </c>
       <c r="CS73" t="inlineStr">
         <is>
@@ -72640,7 +72928,7 @@
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
@@ -72655,42 +72943,42 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
@@ -72889,11 +73177,15 @@
           <t>37.07000000000001</t>
         </is>
       </c>
-      <c r="CQ74" t="n">
-        <v>36.46</v>
-      </c>
-      <c r="CR74" t="n">
-        <v>34.12</v>
+      <c r="CQ74" t="inlineStr">
+        <is>
+          <t>36.46</t>
+        </is>
+      </c>
+      <c r="CR74" t="inlineStr">
+        <is>
+          <t>34.12</t>
+        </is>
       </c>
       <c r="CS74" t="inlineStr">
         <is>
@@ -73646,7 +73938,7 @@
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
@@ -73656,27 +73948,27 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
@@ -73875,11 +74167,15 @@
           <t>36.6</t>
         </is>
       </c>
-      <c r="CQ75" t="n">
-        <v>36.31</v>
-      </c>
-      <c r="CR75" t="n">
-        <v>34.02</v>
+      <c r="CQ75" t="inlineStr">
+        <is>
+          <t>36.31</t>
+        </is>
+      </c>
+      <c r="CR75" t="inlineStr">
+        <is>
+          <t>34.02</t>
+        </is>
       </c>
       <c r="CS75" t="inlineStr">
         <is>
@@ -74607,62 +74903,62 @@
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr">
+      <c r="AW76" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AT76" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV76" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
@@ -74861,11 +75157,15 @@
           <t>36.185</t>
         </is>
       </c>
-      <c r="CQ76" t="n">
-        <v>36.22</v>
-      </c>
-      <c r="CR76" t="n">
-        <v>33.91</v>
+      <c r="CQ76" t="inlineStr">
+        <is>
+          <t>36.22</t>
+        </is>
+      </c>
+      <c r="CR76" t="inlineStr">
+        <is>
+          <t>33.91</t>
+        </is>
       </c>
       <c r="CS76" t="inlineStr">
         <is>
@@ -75593,62 +75893,62 @@
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV77" t="inlineStr">
+      <c r="AW77" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW77" t="inlineStr">
+      <c r="AX77" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
+      <c r="AY77" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
@@ -75847,11 +76147,15 @@
           <t>35.815</t>
         </is>
       </c>
-      <c r="CQ77" t="n">
-        <v>36.05</v>
-      </c>
-      <c r="CR77" t="n">
-        <v>33.76</v>
+      <c r="CQ77" t="inlineStr">
+        <is>
+          <t>36.05</t>
+        </is>
+      </c>
+      <c r="CR77" t="inlineStr">
+        <is>
+          <t>33.76</t>
+        </is>
       </c>
       <c r="CS77" t="inlineStr">
         <is>
@@ -76599,42 +76903,42 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV78" t="inlineStr">
+      <c r="AW78" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW78" t="inlineStr">
+      <c r="AX78" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
+      <c r="AY78" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
@@ -76833,11 +77137,15 @@
           <t>35.61499999999999</t>
         </is>
       </c>
-      <c r="CQ78" t="n">
-        <v>36.01</v>
-      </c>
-      <c r="CR78" t="n">
-        <v>33.69</v>
+      <c r="CQ78" t="inlineStr">
+        <is>
+          <t>36.01</t>
+        </is>
+      </c>
+      <c r="CR78" t="inlineStr">
+        <is>
+          <t>33.69</t>
+        </is>
       </c>
       <c r="CS78" t="inlineStr">
         <is>
@@ -77585,42 +77893,42 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV79" t="inlineStr">
+      <c r="AW79" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW79" t="inlineStr">
+      <c r="AX79" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
+      <c r="AY79" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
@@ -77819,11 +78127,15 @@
           <t>35.485</t>
         </is>
       </c>
-      <c r="CQ79" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>33.67</v>
+      <c r="CQ79" t="inlineStr">
+        <is>
+          <t>35.9</t>
+        </is>
+      </c>
+      <c r="CR79" t="inlineStr">
+        <is>
+          <t>33.67</t>
+        </is>
       </c>
       <c r="CS79" t="inlineStr">
         <is>
@@ -78576,7 +78888,7 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
@@ -78591,22 +78903,22 @@
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
@@ -78805,11 +79117,15 @@
           <t>35.40499999999999</t>
         </is>
       </c>
-      <c r="CQ80" t="n">
-        <v>35.74</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>33.66</v>
+      <c r="CQ80" t="inlineStr">
+        <is>
+          <t>35.74</t>
+        </is>
+      </c>
+      <c r="CR80" t="inlineStr">
+        <is>
+          <t>33.66</t>
+        </is>
       </c>
       <c r="CS80" t="inlineStr">
         <is>
@@ -79562,7 +79878,7 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
@@ -79577,22 +79893,22 @@
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
@@ -79791,11 +80107,15 @@
           <t>35.45</t>
         </is>
       </c>
-      <c r="CQ81" t="n">
-        <v>35.58</v>
-      </c>
-      <c r="CR81" t="n">
-        <v>33.63</v>
+      <c r="CQ81" t="inlineStr">
+        <is>
+          <t>35.58</t>
+        </is>
+      </c>
+      <c r="CR81" t="inlineStr">
+        <is>
+          <t>33.63</t>
+        </is>
       </c>
       <c r="CS81" t="inlineStr">
         <is>
@@ -80548,7 +80868,7 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
@@ -80563,22 +80883,22 @@
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
@@ -80777,11 +81097,15 @@
           <t>35.51</t>
         </is>
       </c>
-      <c r="CQ82" t="n">
-        <v>35.44</v>
-      </c>
-      <c r="CR82" t="n">
-        <v>33.64</v>
+      <c r="CQ82" t="inlineStr">
+        <is>
+          <t>35.44</t>
+        </is>
+      </c>
+      <c r="CR82" t="inlineStr">
+        <is>
+          <t>33.64</t>
+        </is>
       </c>
       <c r="CS82" t="inlineStr">
         <is>
